--- a/data/shu_alokasi.xlsx
+++ b/data/shu_alokasi.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -430,7 +430,7 @@
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
     <col width="50" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
@@ -539,7 +539,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Disetujui</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -592,12 +592,118 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Draft</t>
+          <t>Disetujui</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>Sumber SHU: Provisi Pinjaman. Tahun: 2026. Pendapatan provisi pinjaman disetujui/lunas: Rp 60,000. Jumlah pinjaman dihitung: 1.
+[AUTO] SHU dihitung otomatis dari pendapatan provisi pinjaman tahun 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>f3fa271d-02b2-477b-8350-d3983f4ce527</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>da020475-2831-4e34-9c3b-3e35542188b1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>9b45d621-bfcb-4546-8162-9cea8e600916</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>AGT-001</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Boseng</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>2060000</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2060000</v>
+      </c>
+      <c r="H4" t="n">
+        <v>154500</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1030000</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1184500</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Sumber SHU: Provisi Pinjaman. Tahun: 2026. Pendapatan provisi pinjaman disetujui/lunas: Rp 2,060,000. Jumlah pinjaman dihitung: 1.
+[AUTO] SHU dihitung otomatis dari pendapatan provisi pinjaman tahun 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>62093732-ff53-4e82-9987-d3bfecd41cb7</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>da020475-2831-4e34-9c3b-3e35542188b1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>AGT-DEMO-001</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>KOP-0001</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Anggota Demo</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>154500</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>154500</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Sumber SHU: Provisi Pinjaman. Tahun: 2026. Pendapatan provisi pinjaman disetujui/lunas: Rp 2,060,000. Jumlah pinjaman dihitung: 1.
 [AUTO] SHU dihitung otomatis dari pendapatan provisi pinjaman tahun 2026.</t>
         </is>
       </c>
